--- a/artfynd/A 3543-2024 artfynd.xlsx
+++ b/artfynd/A 3543-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>121138826</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3543-2024 artfynd.xlsx
+++ b/artfynd/A 3543-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121139068</v>
+        <v>121138826</v>
       </c>
       <c r="B2" t="n">
-        <v>39842</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>214803</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333602</v>
+        <v>333656</v>
       </c>
       <c r="R2" t="n">
-        <v>6403510</v>
+        <v>6403468</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,18 +761,12 @@
           <t>2024-08-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kläckhål på björk</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121138826</v>
+        <v>121139068</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>39842</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +797,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>214803</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333656</v>
+        <v>333602</v>
       </c>
       <c r="R3" t="n">
-        <v>6403468</v>
+        <v>6403510</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,12 +872,18 @@
           <t>2024-08-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3543-2024 artfynd.xlsx
+++ b/artfynd/A 3543-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121138826</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>121139068</v>
       </c>
       <c r="B3" t="n">
-        <v>39842</v>
+        <v>39845</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3543-2024 artfynd.xlsx
+++ b/artfynd/A 3543-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>121138826</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -785,37 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121139068</v>
+        <v>121139013</v>
       </c>
       <c r="B3" t="n">
-        <v>39845</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>214803</v>
+        <v>102204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333602</v>
+        <v>333366</v>
       </c>
       <c r="R3" t="n">
-        <v>6403510</v>
+        <v>6403623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,17 +854,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>kläckhål på björk</t>
+          <t>gnag och kläckhål på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,6 +889,335 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126384730</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lindås, Lindås, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>333342</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6403478</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Westas janco</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emma Westas janco</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126384889</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lindås, Lindås, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>333343</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6403476</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Westas janco</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Westas janco</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121139068</v>
+      </c>
+      <c r="B6" t="n">
+        <v>40300</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>214803</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dolkstekelsglasvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Synanthedon scoliaeformis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lerum, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>333602</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6403510</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>kläckhål på björk</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3543-2024 artfynd.xlsx
+++ b/artfynd/A 3543-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121138826</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121139013</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126384730</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126384889</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,8 +1243,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121139068</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>